--- a/docs/01_overview/【部会用】進捗確認 _開発 .xlsx
+++ b/docs/01_overview/【部会用】進捗確認 _開発 .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\enjoy\06_システム開発部活動\第12期\個人目標\開発\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktakw\sg-mock-test-system\docs\01_overview\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E53959-6B70-4295-A921-9F67A06ADF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-8655" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="開発スケジュール" sheetId="2" r:id="rId1"/>
@@ -938,16 +938,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -964,6 +958,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1249,47 +1249,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60B6E7C5-2D2D-48FD-81BD-EED9B2259812}">
   <dimension ref="B2:I48"/>
-  <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.09765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.125" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" customWidth="1"/>
     <col min="5" max="5" width="73.5" bestFit="1" customWidth="1"/>
     <col min="6" max="9" width="14.5" customWidth="1"/>
     <col min="10" max="10" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="1" t="s">
@@ -1336,9 +1336,9 @@
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="5" t="s">
         <v>32</v>
       </c>
@@ -1348,8 +1348,8 @@
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
       <c r="D9" s="7" t="s">
         <v>19</v>
       </c>
@@ -1362,9 +1362,9 @@
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="2:9">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
       <c r="E10" s="5" t="s">
         <v>33</v>
       </c>
@@ -1392,9 +1392,9 @@
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
       <c r="E12" s="5" t="s">
         <v>35</v>
       </c>
@@ -1404,9 +1404,9 @@
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="5" t="s">
         <v>37</v>
       </c>
@@ -1416,9 +1416,9 @@
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
       <c r="E14" s="5" t="s">
         <v>38</v>
       </c>
@@ -1428,8 +1428,8 @@
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
       <c r="D15" s="7" t="s">
         <v>20</v>
       </c>
@@ -1442,9 +1442,9 @@
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="4" t="s">
         <v>41</v>
       </c>
@@ -1454,9 +1454,9 @@
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="4" t="s">
         <v>40</v>
       </c>
@@ -1484,9 +1484,9 @@
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="4" t="s">
         <v>42</v>
       </c>
@@ -1496,9 +1496,9 @@
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="9"/>
       <c r="E20" s="4" t="s">
         <v>44</v>
       </c>
@@ -1508,8 +1508,8 @@
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
       <c r="D21" s="7" t="s">
         <v>23</v>
       </c>
@@ -1522,9 +1522,9 @@
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
       <c r="E22" s="4" t="s">
         <v>46</v>
       </c>
@@ -1534,9 +1534,9 @@
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="9"/>
       <c r="E23" s="4" t="s">
         <v>47</v>
       </c>
@@ -1546,8 +1546,8 @@
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
       <c r="D24" s="7" t="s">
         <v>22</v>
       </c>
@@ -1560,9 +1560,9 @@
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
       <c r="E25" s="4" t="s">
         <v>49</v>
       </c>
@@ -1572,13 +1572,13 @@
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="4" t="s">
@@ -1590,9 +1590,9 @@
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="13"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="15"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="13"/>
       <c r="E27" s="4" t="s">
         <v>52</v>
       </c>
@@ -1602,9 +1602,9 @@
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="13"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="15"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="13"/>
       <c r="E28" s="4" t="s">
         <v>53</v>
       </c>
@@ -1614,9 +1614,9 @@
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="13"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="15"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="13"/>
       <c r="E29" s="5" t="s">
         <v>54</v>
       </c>
@@ -1626,9 +1626,9 @@
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="13"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="15"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="13"/>
       <c r="E30" s="4" t="s">
         <v>55</v>
       </c>
@@ -1638,9 +1638,9 @@
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="13"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="15"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="13"/>
       <c r="E31" s="4" t="s">
         <v>56</v>
       </c>
@@ -1650,9 +1650,9 @@
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="13"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="15"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="13"/>
       <c r="E32" s="4" t="s">
         <v>57</v>
       </c>
@@ -1662,9 +1662,9 @@
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="13"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="15"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="13"/>
       <c r="E33" s="4" t="s">
         <v>58</v>
       </c>
@@ -1674,13 +1674,13 @@
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="4" t="s">
@@ -1692,9 +1692,9 @@
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="16"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="15"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="13"/>
       <c r="E35" s="4" t="s">
         <v>61</v>
       </c>
@@ -1704,9 +1704,9 @@
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="16"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="15"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="13"/>
       <c r="E36" s="4" t="s">
         <v>62</v>
       </c>
@@ -1716,9 +1716,9 @@
       <c r="I36" s="4"/>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="16"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="15"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="13"/>
       <c r="E37" s="4" t="s">
         <v>63</v>
       </c>
@@ -1728,9 +1728,9 @@
       <c r="I37" s="4"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="16"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="15"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="13"/>
       <c r="E38" s="4" t="s">
         <v>64</v>
       </c>
@@ -1758,9 +1758,9 @@
       <c r="I39" s="4"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
       <c r="E40" s="4" t="s">
         <v>69</v>
       </c>
@@ -1770,9 +1770,9 @@
       <c r="I40" s="4"/>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
       <c r="E41" s="4" t="s">
         <v>68</v>
       </c>
@@ -1800,9 +1800,9 @@
       <c r="I42" s="4"/>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
       <c r="E43" s="4" t="s">
         <v>69</v>
       </c>
@@ -1812,9 +1812,9 @@
       <c r="I43" s="4"/>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
       <c r="E44" s="4" t="s">
         <v>68</v>
       </c>
@@ -1878,9 +1878,9 @@
       <c r="I47" s="4"/>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
       <c r="E48" s="5" t="s">
         <v>77</v>
       </c>
@@ -1891,19 +1891,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="C26:C33"/>
-    <mergeCell ref="D26:D33"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="C47:C48"/>
     <mergeCell ref="D47:D48"/>
@@ -1920,6 +1907,19 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="B18:B25"/>
     <mergeCell ref="C18:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="C26:C33"/>
+    <mergeCell ref="D26:D33"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/01_overview/【部会用】進捗確認 _開発 .xlsx
+++ b/docs/01_overview/【部会用】進捗確認 _開発 .xlsx
@@ -938,10 +938,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -958,12 +964,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1260,36 +1260,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="1" t="s">
@@ -1336,9 +1336,9 @@
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="8"/>
       <c r="E8" s="5" t="s">
         <v>32</v>
       </c>
@@ -1348,8 +1348,8 @@
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
       <c r="D9" s="7" t="s">
         <v>19</v>
       </c>
@@ -1362,9 +1362,9 @@
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="2:9">
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="5" t="s">
         <v>33</v>
       </c>
@@ -1392,9 +1392,9 @@
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
       <c r="E12" s="5" t="s">
         <v>35</v>
       </c>
@@ -1404,9 +1404,9 @@
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
       <c r="E13" s="5" t="s">
         <v>37</v>
       </c>
@@ -1416,9 +1416,9 @@
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="5" t="s">
         <v>38</v>
       </c>
@@ -1428,8 +1428,8 @@
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
       <c r="D15" s="7" t="s">
         <v>20</v>
       </c>
@@ -1442,9 +1442,9 @@
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
       <c r="E16" s="4" t="s">
         <v>41</v>
       </c>
@@ -1454,9 +1454,9 @@
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="4" t="s">
         <v>40</v>
       </c>
@@ -1484,9 +1484,9 @@
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
       <c r="E19" s="4" t="s">
         <v>42</v>
       </c>
@@ -1496,9 +1496,9 @@
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="8"/>
       <c r="E20" s="4" t="s">
         <v>44</v>
       </c>
@@ -1508,8 +1508,8 @@
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
       <c r="D21" s="7" t="s">
         <v>23</v>
       </c>
@@ -1522,9 +1522,9 @@
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
       <c r="E22" s="4" t="s">
         <v>46</v>
       </c>
@@ -1534,9 +1534,9 @@
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="8"/>
       <c r="E23" s="4" t="s">
         <v>47</v>
       </c>
@@ -1546,8 +1546,8 @@
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
       <c r="D24" s="7" t="s">
         <v>22</v>
       </c>
@@ -1560,9 +1560,9 @@
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
       <c r="E25" s="4" t="s">
         <v>49</v>
       </c>
@@ -1572,13 +1572,13 @@
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="12" t="s">
         <v>50</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="14" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="4" t="s">
@@ -1590,9 +1590,9 @@
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="11"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="15"/>
       <c r="E27" s="4" t="s">
         <v>52</v>
       </c>
@@ -1602,9 +1602,9 @@
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="11"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="15"/>
       <c r="E28" s="4" t="s">
         <v>53</v>
       </c>
@@ -1614,9 +1614,9 @@
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="11"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="15"/>
       <c r="E29" s="5" t="s">
         <v>54</v>
       </c>
@@ -1626,9 +1626,9 @@
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="11"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="15"/>
       <c r="E30" s="4" t="s">
         <v>55</v>
       </c>
@@ -1638,9 +1638,9 @@
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="11"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="15"/>
       <c r="E31" s="4" t="s">
         <v>56</v>
       </c>
@@ -1650,9 +1650,9 @@
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="11"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="15"/>
       <c r="E32" s="4" t="s">
         <v>57</v>
       </c>
@@ -1662,9 +1662,9 @@
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="11"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="15"/>
       <c r="E33" s="4" t="s">
         <v>58</v>
       </c>
@@ -1674,13 +1674,13 @@
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="14" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="4" t="s">
@@ -1692,9 +1692,9 @@
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="14"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="13"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="15"/>
       <c r="E35" s="4" t="s">
         <v>61</v>
       </c>
@@ -1704,9 +1704,9 @@
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="14"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="13"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="15"/>
       <c r="E36" s="4" t="s">
         <v>62</v>
       </c>
@@ -1716,9 +1716,9 @@
       <c r="I36" s="4"/>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="14"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="13"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="15"/>
       <c r="E37" s="4" t="s">
         <v>63</v>
       </c>
@@ -1728,9 +1728,9 @@
       <c r="I37" s="4"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="14"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="13"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="15"/>
       <c r="E38" s="4" t="s">
         <v>64</v>
       </c>
@@ -1758,9 +1758,9 @@
       <c r="I39" s="4"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
       <c r="E40" s="4" t="s">
         <v>69</v>
       </c>
@@ -1770,9 +1770,9 @@
       <c r="I40" s="4"/>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
       <c r="E41" s="4" t="s">
         <v>68</v>
       </c>
@@ -1800,9 +1800,9 @@
       <c r="I42" s="4"/>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
       <c r="E43" s="4" t="s">
         <v>69</v>
       </c>
@@ -1812,9 +1812,9 @@
       <c r="I43" s="4"/>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
       <c r="E44" s="4" t="s">
         <v>68</v>
       </c>
@@ -1878,9 +1878,9 @@
       <c r="I47" s="4"/>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
       <c r="E48" s="5" t="s">
         <v>77</v>
       </c>
@@ -1891,6 +1891,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="C26:C33"/>
+    <mergeCell ref="D26:D33"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="C47:C48"/>
     <mergeCell ref="D47:D48"/>
@@ -1907,19 +1920,6 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="B18:B25"/>
     <mergeCell ref="C18:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="C26:C33"/>
-    <mergeCell ref="D26:D33"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/01_overview/【部会用】進捗確認 _開発 .xlsx
+++ b/docs/01_overview/【部会用】進捗確認 _開発 .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktakw\sg-mock-test-system\docs\01_overview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E53959-6B70-4295-A921-9F67A06ADF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605B524E-CE8D-4CFD-8908-0B5394C04056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="開発スケジュール" sheetId="2" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -938,16 +936,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -964,6 +956,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1260,36 +1258,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="1" t="s">
@@ -1336,9 +1334,9 @@
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="5" t="s">
         <v>32</v>
       </c>
@@ -1348,8 +1346,8 @@
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="2:9">
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
       <c r="D9" s="7" t="s">
         <v>19</v>
       </c>
@@ -1362,9 +1360,9 @@
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="2:9">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
       <c r="E10" s="5" t="s">
         <v>33</v>
       </c>
@@ -1392,9 +1390,9 @@
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="2:9">
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
       <c r="E12" s="5" t="s">
         <v>35</v>
       </c>
@@ -1404,9 +1402,9 @@
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="2:9">
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="5" t="s">
         <v>37</v>
       </c>
@@ -1416,9 +1414,9 @@
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="2:9">
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
       <c r="E14" s="5" t="s">
         <v>38</v>
       </c>
@@ -1428,8 +1426,8 @@
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
       <c r="D15" s="7" t="s">
         <v>20</v>
       </c>
@@ -1442,9 +1440,9 @@
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="2:9">
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="4" t="s">
         <v>41</v>
       </c>
@@ -1454,9 +1452,9 @@
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="4" t="s">
         <v>40</v>
       </c>
@@ -1484,9 +1482,9 @@
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="2:9">
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="4" t="s">
         <v>42</v>
       </c>
@@ -1496,9 +1494,9 @@
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="2:9">
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="9"/>
       <c r="E20" s="4" t="s">
         <v>44</v>
       </c>
@@ -1508,8 +1506,8 @@
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="2:9">
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
       <c r="D21" s="7" t="s">
         <v>23</v>
       </c>
@@ -1522,9 +1520,9 @@
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
       <c r="E22" s="4" t="s">
         <v>46</v>
       </c>
@@ -1534,9 +1532,9 @@
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="9"/>
       <c r="E23" s="4" t="s">
         <v>47</v>
       </c>
@@ -1546,8 +1544,8 @@
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
       <c r="D24" s="7" t="s">
         <v>22</v>
       </c>
@@ -1560,9 +1558,9 @@
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
       <c r="E25" s="4" t="s">
         <v>49</v>
       </c>
@@ -1572,13 +1570,13 @@
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="4" t="s">
@@ -1590,9 +1588,9 @@
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="13"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="15"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="13"/>
       <c r="E27" s="4" t="s">
         <v>52</v>
       </c>
@@ -1602,9 +1600,9 @@
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="13"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="15"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="13"/>
       <c r="E28" s="4" t="s">
         <v>53</v>
       </c>
@@ -1614,9 +1612,9 @@
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="13"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="15"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="13"/>
       <c r="E29" s="5" t="s">
         <v>54</v>
       </c>
@@ -1626,9 +1624,9 @@
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="13"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="15"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="13"/>
       <c r="E30" s="4" t="s">
         <v>55</v>
       </c>
@@ -1638,9 +1636,9 @@
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="13"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="15"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="13"/>
       <c r="E31" s="4" t="s">
         <v>56</v>
       </c>
@@ -1650,9 +1648,9 @@
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="13"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="15"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="13"/>
       <c r="E32" s="4" t="s">
         <v>57</v>
       </c>
@@ -1662,9 +1660,9 @@
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="13"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="15"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="13"/>
       <c r="E33" s="4" t="s">
         <v>58</v>
       </c>
@@ -1674,13 +1672,13 @@
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="4" t="s">
@@ -1692,9 +1690,9 @@
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="16"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="15"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="13"/>
       <c r="E35" s="4" t="s">
         <v>61</v>
       </c>
@@ -1704,9 +1702,9 @@
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="16"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="15"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="13"/>
       <c r="E36" s="4" t="s">
         <v>62</v>
       </c>
@@ -1716,9 +1714,9 @@
       <c r="I36" s="4"/>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="16"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="15"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="13"/>
       <c r="E37" s="4" t="s">
         <v>63</v>
       </c>
@@ -1728,9 +1726,9 @@
       <c r="I37" s="4"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="16"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="15"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="13"/>
       <c r="E38" s="4" t="s">
         <v>64</v>
       </c>
@@ -1758,9 +1756,9 @@
       <c r="I39" s="4"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
       <c r="E40" s="4" t="s">
         <v>69</v>
       </c>
@@ -1770,9 +1768,9 @@
       <c r="I40" s="4"/>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
       <c r="E41" s="4" t="s">
         <v>68</v>
       </c>
@@ -1800,9 +1798,9 @@
       <c r="I42" s="4"/>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
       <c r="E43" s="4" t="s">
         <v>69</v>
       </c>
@@ -1812,9 +1810,9 @@
       <c r="I43" s="4"/>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
       <c r="E44" s="4" t="s">
         <v>68</v>
       </c>
@@ -1878,9 +1876,9 @@
       <c r="I47" s="4"/>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
       <c r="E48" s="5" t="s">
         <v>77</v>
       </c>
@@ -1891,19 +1889,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="C26:C33"/>
-    <mergeCell ref="D26:D33"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="C47:C48"/>
     <mergeCell ref="D47:D48"/>
@@ -1920,6 +1905,19 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="B18:B25"/>
     <mergeCell ref="C18:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="C26:C33"/>
+    <mergeCell ref="D26:D33"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
